--- a/assignment3/data/trainingdataset_ontario_budgets_v11_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v11_llm_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E28A3C3-70DD-BC4E-8AE9-01B5E21D14A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9DAD37-C655-F640-91C5-CDDC26D8D41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="500" windowWidth="36440" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
@@ -3792,7 +3792,7 @@
     <t>class_intensity_combined</t>
   </si>
   <si>
-    <t>class_intensity_combined_#</t>
+    <t>class_intensity_high_low</t>
   </si>
 </sst>
 </file>
@@ -4332,7 +4332,8 @@
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="5" width="15" style="13" customWidth="1"/>
-    <col min="6" max="7" width="23.5" style="13" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="13" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="13" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16.5" customWidth="1"/>
